--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>109993</v>
+        <v>110011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110011</v>
+        <v>110013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110013</v>
+        <v>110020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110020</v>
+        <v>110029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110729</v>
+        <v>110732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110732</v>
+        <v>110819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110819</v>
+        <v>110822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110822</v>
+        <v>110848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110848</v>
+        <v>110849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110849</v>
+        <v>110850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37286-2021 artfynd.xlsx
+++ b/artfynd/A 37286-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121739471</v>
       </c>
       <c r="B2" t="n">
-        <v>110850</v>
+        <v>111128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
